--- a/RMUTL_WORK/Teaching work/2025/เทอม_02/ENGCE117_Computer Programming for Computer Engineer/CHECK_LIST_117.xlsx
+++ b/RMUTL_WORK/Teaching work/2025/เทอม_02/ENGCE117_Computer Programming for Computer Engineer/CHECK_LIST_117.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LOBSTER69\Documents\GitHub\WORK\RMUTL_WORK\Teaching work\2025\เทอม_02\ENGCE117_Computer Programming for Computer Engineer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1916B0F4-45FE-48FC-9016-F23EEEAA5258}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D921CFB-C157-47ED-8033-F805A3966732}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
